--- a/src/examples/ELV/data/ELV_ICE_compositions.xlsx
+++ b/src/examples/ELV/data/ELV_ICE_compositions.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="ELV_ICE-prd" sheetId="1" state="visible" r:id="rId2"/>
@@ -17,15 +17,23 @@
     <sheet name="ELV_ICE_batt-cpt" sheetId="7" state="visible" r:id="rId8"/>
     <sheet name="ELV_ICE_nonferrous-mat" sheetId="8" state="visible" r:id="rId9"/>
     <sheet name="ELV_ICE_ferrous-mat" sheetId="9" state="visible" r:id="rId10"/>
+    <sheet name="ELV_ICE_rubber-mat" sheetId="10" state="visible" r:id="rId11"/>
+    <sheet name="ELV_ICE_ree-mat" sheetId="11" state="visible" r:id="rId12"/>
+    <sheet name="ELV_ICE_H2SO4-cmp" sheetId="12" state="visible" r:id="rId13"/>
+    <sheet name="ELV_ICE_Pb-elm" sheetId="13" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_batt-cpt'!$A$1:$E$3</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_body-cpt'!$A$1:$E$5</definedName>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_catconv-cpt'!$A$1:$E$4</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_catconv-cpt'!$A$1:$E$2</definedName>
     <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_elec-cpt'!$A$1:$E$4</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_engtrans-cpt'!$A$1:$E$4</definedName>
     <definedName function="false" hidden="true" localSheetId="8" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_ferrous-mat'!$A$1:$E$4</definedName>
+    <definedName function="false" hidden="true" localSheetId="11" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_H2SO4-cmp'!$A$1:$E$2</definedName>
     <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_nonferrous-mat'!$A$1:$E$4</definedName>
+    <definedName function="false" hidden="true" localSheetId="12" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_Pb-elm'!$A$1:$E$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="10" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_ree-mat'!$A$1:$E$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="9" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_rubber-mat'!$A$1:$E$2</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_tyres-cpt'!$A$1:$E$3</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
@@ -38,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="41">
   <si>
     <t xml:space="preserve">fraction</t>
   </si>
@@ -97,67 +105,70 @@
     <t xml:space="preserve">rest</t>
   </si>
   <si>
+    <t xml:space="preserve">ree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rubber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">element</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Au</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plastic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H2SO4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">compound</t>
+  </si>
+  <si>
+    <t xml:space="preserve">brass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mn</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pt</t>
   </si>
   <si>
-    <t xml:space="preserve">element</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pd</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rh</t>
   </si>
   <si>
     <t xml:space="preserve">Ce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rubber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Al</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Au</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">plastic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H2SO4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">compound</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mn</t>
   </si>
 </sst>
 </file>
@@ -290,6 +301,18 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
@@ -315,6 +338,10 @@
 </file>
 
 <file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
@@ -557,6 +584,376 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="34.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="2" width="16.69"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <f aca="false">SUM(D2:D2)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C6" s="3"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E2"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="34.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="2" width="16.69"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <f aca="false">D2*$C$7</f>
+        <v>1.085</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <f aca="false">D3*$C$7</f>
+        <v>1.085</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <f aca="false">D4*$C$7</f>
+        <v>2.17</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <f aca="false">D5*$C$7</f>
+        <v>10.85</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <f aca="false">D6*$C$7</f>
+        <v>6.51</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <f aca="false">SUM(D2:D6)</f>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E2"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="34.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="2" width="16.69"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <f aca="false">SUM(D2:D2)</f>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E2"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="34.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="2" width="16.69"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <f aca="false">SUM(D2:D2)</f>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E2"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -911,7 +1308,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="34.47"/>
@@ -937,54 +1334,54 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <f aca="false">'ELV_ICE-prd'!C$4*D2</f>
-        <v>3.5</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0.05</v>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <f aca="false">0.31*70</f>
+        <v>21.7</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>0.31</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>20</v>
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C3" s="3" t="n">
         <f aca="false">'ELV_ICE-prd'!C$4*D3</f>
-        <v>3.5</v>
+        <v>41.3</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.05</v>
+        <v>0.59</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>20</v>
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="n">
         <f aca="false">'ELV_ICE-prd'!C$4*D4</f>
-        <v>0.7</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0.1</v>
@@ -992,70 +1389,25 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <f aca="false">'ELV_ICE-prd'!C$4*D5</f>
-        <v>14</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <f aca="false">'ELV_ICE-prd'!C$4*D6</f>
-        <v>41.3</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <f aca="false">'ELV_ICE-prd'!C$4*D7</f>
-        <v>7</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C5" s="2" t="n">
         <f aca="false">'ELV_ICE-prd'!C4</f>
         <v>70</v>
       </c>
-      <c r="D8" s="2" t="n">
-        <f aca="false">SUM(D2:D7)</f>
-        <v>1</v>
-      </c>
+      <c r="D5" s="2" t="n">
+        <f aca="false">SUM(D2:D4)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C9" s="3"/>
@@ -1066,17 +1418,8 @@
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C11" s="3"/>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="3"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="3"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E4"/>
+  <autoFilter ref="A1:E2"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1138,7 +1481,7 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>15</v>
@@ -1221,10 +1564,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3" t="n">
         <f aca="false">'ELV_ICE-prd'!C$6*D2</f>
@@ -1239,10 +1582,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C3" s="3" t="n">
         <f aca="false">'ELV_ICE-prd'!C$6*D3</f>
@@ -1257,10 +1600,10 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="n">
         <f aca="false">'ELV_ICE-prd'!C$6*D4</f>
@@ -1275,10 +1618,10 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3" t="n">
         <f aca="false">'ELV_ICE-prd'!C$6*D5</f>
@@ -1293,10 +1636,10 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C6" s="3" t="n">
         <f aca="false">'ELV_ICE-prd'!C$6*D6</f>
@@ -1311,10 +1654,10 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C7" s="3" t="n">
         <f aca="false">'ELV_ICE-prd'!C$6*D7</f>
@@ -1329,10 +1672,10 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C8" s="3" t="n">
         <f aca="false">'ELV_ICE-prd'!C$6*D8</f>
@@ -1347,10 +1690,10 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C9" s="3" t="n">
         <f aca="false">'ELV_ICE-prd'!C$6*D9</f>
@@ -1365,7 +1708,7 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>15</v>
@@ -1448,10 +1791,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3" t="n">
         <f aca="false">C$5*D2</f>
@@ -1466,10 +1809,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C3" s="3" t="n">
         <f aca="false">C$5*D3</f>
@@ -1484,7 +1827,7 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>15</v>
@@ -1567,10 +1910,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3" t="n">
         <f aca="false">$C$11*D2</f>
@@ -1585,10 +1928,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C3" s="3" t="n">
         <f aca="false">$C$11*D3</f>
@@ -1603,10 +1946,10 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="n">
         <f aca="false">$C$11*D4</f>
@@ -1621,10 +1964,10 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3" t="n">
         <f aca="false">$C$11*D5</f>
@@ -1639,10 +1982,10 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C6" s="3" t="n">
         <f aca="false">$C$11*D6</f>
@@ -1657,10 +2000,10 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C7" s="3" t="n">
         <f aca="false">$C$11*D7</f>
@@ -1675,10 +2018,10 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C8" s="3" t="n">
         <f aca="false">$C$11*D8</f>
@@ -1693,10 +2036,10 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C9" s="3" t="n">
         <f aca="false">$C$11*D9</f>
@@ -1794,10 +2137,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3" t="n">
         <f aca="false">$C$6*D2</f>
@@ -1812,10 +2155,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C3" s="3" t="n">
         <f aca="false">$C$6*D3</f>
@@ -1830,10 +2173,10 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="n">
         <f aca="false">$C$6*D4</f>
@@ -1869,7 +2212,7 @@
         <v>13</v>
       </c>
       <c r="C6" s="3" t="n">
-        <f aca="false">'ELV_ICE_engtrans-cpt'!C2+'ELV_ICE_body-cpt'!C2+'ELV_ICE_catconv-cpt'!C6</f>
+        <f aca="false">'ELV_ICE_engtrans-cpt'!C2+'ELV_ICE_body-cpt'!C2+'ELV_ICE_catconv-cpt'!C3</f>
         <v>904.4</v>
       </c>
       <c r="D6" s="2" t="n">

--- a/src/examples/ELV/data/ELV_ICE_compositions.xlsx
+++ b/src/examples/ELV/data/ELV_ICE_compositions.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="12"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="17"/>
   </bookViews>
   <sheets>
     <sheet name="ELV_ICE-prd" sheetId="1" state="visible" r:id="rId2"/>
@@ -14,27 +14,41 @@
     <sheet name="ELV_ICE_catconv-cpt" sheetId="4" state="visible" r:id="rId5"/>
     <sheet name="ELV_ICE_tyres-cpt" sheetId="5" state="visible" r:id="rId6"/>
     <sheet name="ELV_ICE_elec-cpt" sheetId="6" state="visible" r:id="rId7"/>
-    <sheet name="ELV_ICE_batt-cpt" sheetId="7" state="visible" r:id="rId8"/>
-    <sheet name="ELV_ICE_nonferrous-mat" sheetId="8" state="visible" r:id="rId9"/>
-    <sheet name="ELV_ICE_ferrous-mat" sheetId="9" state="visible" r:id="rId10"/>
-    <sheet name="ELV_ICE_rubber-mat" sheetId="10" state="visible" r:id="rId11"/>
-    <sheet name="ELV_ICE_ree-mat" sheetId="11" state="visible" r:id="rId12"/>
-    <sheet name="ELV_ICE_H2SO4-cmp" sheetId="12" state="visible" r:id="rId13"/>
-    <sheet name="ELV_ICE_Pb-elm" sheetId="13" state="visible" r:id="rId14"/>
+    <sheet name="ELV_ICE_liquids-mat" sheetId="7" state="visible" r:id="rId8"/>
+    <sheet name="ELV_ICE_batt-cpt" sheetId="8" state="visible" r:id="rId9"/>
+    <sheet name="ELV_ICE_nonferrous-mat" sheetId="9" state="visible" r:id="rId10"/>
+    <sheet name="ELV_ICE_slag_nfe-mat" sheetId="10" state="visible" r:id="rId11"/>
+    <sheet name="ELV_ICE_ferrous-mat" sheetId="11" state="visible" r:id="rId12"/>
+    <sheet name="ELV_ICE_slag_fe-mat" sheetId="12" state="visible" r:id="rId13"/>
+    <sheet name="ELV_ICE_rubber-mat" sheetId="13" state="visible" r:id="rId14"/>
+    <sheet name="ELV_ICE_ree-mat" sheetId="14" state="visible" r:id="rId15"/>
+    <sheet name="ELV_ICE_slag_ree-mat" sheetId="15" state="visible" r:id="rId16"/>
+    <sheet name="ELV_ICE_glass-mat" sheetId="16" state="visible" r:id="rId17"/>
+    <sheet name="ELV_ICE_waste_shredder-mat" sheetId="17" state="visible" r:id="rId18"/>
+    <sheet name="ELV_ICE_plastic-mat" sheetId="18" state="visible" r:id="rId19"/>
+    <sheet name="ELV_ICE_H2SO4-cmp" sheetId="19" state="visible" r:id="rId20"/>
+    <sheet name="ELV_ICE_Pb-elm" sheetId="20" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_batt-cpt'!$A$1:$E$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_batt-cpt'!$A$1:$E$3</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_body-cpt'!$A$1:$E$5</definedName>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_catconv-cpt'!$A$1:$E$2</definedName>
     <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_elec-cpt'!$A$1:$E$4</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_engtrans-cpt'!$A$1:$E$4</definedName>
-    <definedName function="false" hidden="true" localSheetId="8" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_ferrous-mat'!$A$1:$E$4</definedName>
-    <definedName function="false" hidden="true" localSheetId="11" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_H2SO4-cmp'!$A$1:$E$2</definedName>
-    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_nonferrous-mat'!$A$1:$E$4</definedName>
-    <definedName function="false" hidden="true" localSheetId="12" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_Pb-elm'!$A$1:$E$2</definedName>
-    <definedName function="false" hidden="true" localSheetId="10" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_ree-mat'!$A$1:$E$2</definedName>
-    <definedName function="false" hidden="true" localSheetId="9" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_rubber-mat'!$A$1:$E$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="10" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_ferrous-mat'!$A$1:$E$4</definedName>
+    <definedName function="false" hidden="true" localSheetId="15" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_glass-mat'!$A$1:$E$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="18" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_H2SO4-cmp'!$A$1:$E$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_liquids-mat'!$A$1:$E$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="8" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_nonferrous-mat'!$A$1:$E$4</definedName>
+    <definedName function="false" hidden="true" localSheetId="19" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_Pb-elm'!$A$1:$E$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="17" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_plastic-mat'!$A$1:$E$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="13" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_ree-mat'!$A$1:$E$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="12" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_rubber-mat'!$A$1:$E$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="11" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_slag_fe-mat'!$A$1:$E$4</definedName>
+    <definedName function="false" hidden="true" localSheetId="9" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_slag_nfe-mat'!$A$1:$E$4</definedName>
+    <definedName function="false" hidden="true" localSheetId="14" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_slag_ree-mat'!$A$1:$E$2</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_tyres-cpt'!$A$1:$E$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="16" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_waste_shredder-mat'!$A$1:$E$2</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -46,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="42">
   <si>
     <t xml:space="preserve">fraction</t>
   </si>
@@ -139,6 +153,9 @@
   </si>
   <si>
     <t xml:space="preserve">plastic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">waste_oil</t>
   </si>
   <si>
     <t xml:space="preserve">H2SO4</t>
@@ -313,6 +330,34 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
@@ -589,6 +634,507 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="34.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="2" width="16.69"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <f aca="false">$C$11*D2</f>
+        <v>19.88</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <f aca="false">$C$11*D3</f>
+        <v>3.976</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <f aca="false">$C$11*D4</f>
+        <v>3.976</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <f aca="false">$C$11*D5</f>
+        <v>1.988</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <f aca="false">$C$11*D6</f>
+        <v>1.988</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <f aca="false">$C$11*D7</f>
+        <v>1.988</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <f aca="false">$C$11*D8</f>
+        <v>1.988</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <f aca="false">$C$11*D9</f>
+        <v>1.988</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <f aca="false">$C$11*D10</f>
+        <v>161.028</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.81</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <f aca="false">'ELV_ICE_engtrans-cpt'!C3+'ELV_ICE_body-cpt'!C3</f>
+        <v>198.8</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <f aca="false">SUM(D2:D10)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C13" s="3"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C14" s="3"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E4"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="34.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="2" width="16.69"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="2" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <f aca="false">$C$6*D2</f>
+        <v>859.18</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <f aca="false">$C$6*D3</f>
+        <v>9.044</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <f aca="false">$C$6*D4</f>
+        <v>9.044</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <f aca="false">$C$6*D5</f>
+        <v>27.132</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <f aca="false">'ELV_ICE_engtrans-cpt'!C2+'ELV_ICE_body-cpt'!C2+'ELV_ICE_catconv-cpt'!C3</f>
+        <v>904.4</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <f aca="false">SUM(D2:D5)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C9" s="3"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E4"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="34.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="2" width="16.69"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <f aca="false">$C$6*D2</f>
+        <v>90.44</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <f aca="false">$C$6*D3</f>
+        <v>9.044</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <f aca="false">$C$6*D4</f>
+        <v>9.044</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <f aca="false">$C$6*D5</f>
+        <v>795.872</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <f aca="false">'ELV_ICE_engtrans-cpt'!C2+'ELV_ICE_body-cpt'!C2+'ELV_ICE_catconv-cpt'!C3</f>
+        <v>904.4</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <f aca="false">SUM(D2:D5)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C9" s="3"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E4"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -665,7 +1211,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -697,7 +1243,7 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>22</v>
@@ -733,7 +1279,7 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>22</v>
@@ -751,7 +1297,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>22</v>
@@ -810,7 +1356,414 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="34.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="2" width="16.69"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <f aca="false">0.31*70</f>
+        <v>21.7</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <f aca="false">'ELV_ICE-prd'!C$4*D3</f>
+        <v>41.3</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <f aca="false">'ELV_ICE-prd'!C$4*D4</f>
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <f aca="false">SUM(D2:D4)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C11" s="3"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E2"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="34.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="2" width="16.69"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <f aca="false">SUM(D2:D2)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C6" s="3"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E2"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="34.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="2" width="16.69"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <f aca="false">D2*$C$5</f>
+        <v>60.9</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <f aca="false">D3*$C$5</f>
+        <v>20.3</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <f aca="false">D4*$C$5</f>
+        <v>20.3</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <f aca="false">SUM(D2:D4)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C8" s="3"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E2"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="34.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="2" width="16.69"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <f aca="false">SUM(D2:D2)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C6" s="3"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E2"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -842,10 +1795,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>7</v>
@@ -882,7 +1835,192 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="16.69"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <f aca="false">'ELV_ICE-prd'!C$2*D2</f>
+        <v>485.1</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <f aca="false">'ELV_ICE-prd'!C$2*D3</f>
+        <v>169.4</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <f aca="false">'ELV_ICE-prd'!C$2*D4</f>
+        <v>30.8</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <f aca="false">'ELV_ICE-prd'!C$2*D5</f>
+        <v>84.7</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="3" t="n">
+        <f aca="false">'ELV_ICE-prd'!C2</f>
+        <v>770</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <f aca="false">SUM(D2:D5)</f>
+        <v>1</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C10" s="4"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C15" s="4"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E5"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -943,191 +2081,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:E2"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
-  </headerFooter>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="16.69"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <f aca="false">'ELV_ICE-prd'!C$2*D2</f>
-        <v>485.1</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <f aca="false">'ELV_ICE-prd'!C$2*D3</f>
-        <v>169.4</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <f aca="false">'ELV_ICE-prd'!C$2*D4</f>
-        <v>30.8</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <f aca="false">'ELV_ICE-prd'!C$2*D5</f>
-        <v>84.7</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3" t="n">
-        <f aca="false">'ELV_ICE-prd'!C2</f>
-        <v>770</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <f aca="false">SUM(D2:D5)</f>
-        <v>1</v>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="4"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="4"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C12" s="4"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="4"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="4"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C15" s="4"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:E5"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1764,6 +2717,88 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="34.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="2" width="16.69"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <f aca="false">'ELV_ICE-prd'!C6</f>
+        <v>28</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <f aca="false">SUM(D2:D2)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C6" s="3"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E2"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -1809,10 +2844,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="3" t="n">
         <f aca="false">C$5*D3</f>
@@ -1878,7 +2913,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1946,7 +2981,7 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>22</v>
@@ -1982,7 +3017,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>22</v>
@@ -2018,7 +3053,7 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>22</v>
@@ -2091,143 +3126,6 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C14" s="3"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:E4"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
-  </headerFooter>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="34.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="2" width="16.69"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="2" width="11.53"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <f aca="false">$C$6*D2</f>
-        <v>859.18</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <f aca="false">$C$6*D3</f>
-        <v>9.044</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <f aca="false">$C$6*D4</f>
-        <v>9.044</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <f aca="false">$C$6*D5</f>
-        <v>27.132</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <f aca="false">'ELV_ICE_engtrans-cpt'!C2+'ELV_ICE_body-cpt'!C2+'ELV_ICE_catconv-cpt'!C3</f>
-        <v>904.4</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <f aca="false">SUM(D2:D5)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="3"/>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C8" s="3"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C9" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E4"/>

--- a/src/examples/ELV/data/ELV_ICE_compositions.xlsx
+++ b/src/examples/ELV/data/ELV_ICE_compositions.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="17"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="ELV_ICE-prd" sheetId="1" state="visible" r:id="rId2"/>
@@ -16,39 +16,43 @@
     <sheet name="ELV_ICE_elec-cpt" sheetId="6" state="visible" r:id="rId7"/>
     <sheet name="ELV_ICE_liquids-mat" sheetId="7" state="visible" r:id="rId8"/>
     <sheet name="ELV_ICE_batt-cpt" sheetId="8" state="visible" r:id="rId9"/>
-    <sheet name="ELV_ICE_nonferrous-mat" sheetId="9" state="visible" r:id="rId10"/>
+    <sheet name="ELV_ICE_nfe-mat" sheetId="9" state="visible" r:id="rId10"/>
     <sheet name="ELV_ICE_slag_nfe-mat" sheetId="10" state="visible" r:id="rId11"/>
-    <sheet name="ELV_ICE_ferrous-mat" sheetId="11" state="visible" r:id="rId12"/>
+    <sheet name="ELV_ICE_fe-mat" sheetId="11" state="visible" r:id="rId12"/>
     <sheet name="ELV_ICE_slag_fe-mat" sheetId="12" state="visible" r:id="rId13"/>
-    <sheet name="ELV_ICE_rubber-mat" sheetId="13" state="visible" r:id="rId14"/>
+    <sheet name="ALL_rubber-mat" sheetId="13" state="visible" r:id="rId14"/>
     <sheet name="ELV_ICE_ree-mat" sheetId="14" state="visible" r:id="rId15"/>
-    <sheet name="ELV_ICE_slag_ree-mat" sheetId="15" state="visible" r:id="rId16"/>
-    <sheet name="ELV_ICE_glass-mat" sheetId="16" state="visible" r:id="rId17"/>
+    <sheet name="ALL_slag_ree-mat" sheetId="15" state="visible" r:id="rId16"/>
+    <sheet name="ALL_glass-mat" sheetId="16" state="visible" r:id="rId17"/>
     <sheet name="ELV_ICE_waste_shredder-mat" sheetId="17" state="visible" r:id="rId18"/>
-    <sheet name="ELV_ICE_plastic-mat" sheetId="18" state="visible" r:id="rId19"/>
-    <sheet name="ELV_ICE_H2SO4-cmp" sheetId="19" state="visible" r:id="rId20"/>
-    <sheet name="ELV_ICE_Pb-elm" sheetId="20" state="visible" r:id="rId21"/>
+    <sheet name="ALL_plastic-mat" sheetId="18" state="visible" r:id="rId19"/>
+    <sheet name="H2SO4-cmp" sheetId="19" state="visible" r:id="rId20"/>
+    <sheet name="Pb-elm" sheetId="20" state="visible" r:id="rId21"/>
+    <sheet name="ELV_ICE_rest-mat" sheetId="21" state="visible" r:id="rId22"/>
+    <sheet name="ELV_ICE_wasteoil-mat" sheetId="22" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames>
+    <definedName function="false" hidden="true" localSheetId="15" name="_xlnm._FilterDatabase" vbProcedure="false">'ALL_glass-mat'!$A$1:$E$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="17" name="_xlnm._FilterDatabase" vbProcedure="false">'ALL_plastic-mat'!$A$1:$E$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="12" name="_xlnm._FilterDatabase" vbProcedure="false">'ALL_rubber-mat'!$A$1:$E$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="14" name="_xlnm._FilterDatabase" vbProcedure="false">'ALL_slag_ree-mat'!$A$1:$E$2</definedName>
     <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_batt-cpt'!$A$1:$E$3</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_body-cpt'!$A$1:$E$5</definedName>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_catconv-cpt'!$A$1:$E$2</definedName>
     <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_elec-cpt'!$A$1:$E$4</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_engtrans-cpt'!$A$1:$E$4</definedName>
-    <definedName function="false" hidden="true" localSheetId="10" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_ferrous-mat'!$A$1:$E$4</definedName>
-    <definedName function="false" hidden="true" localSheetId="15" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_glass-mat'!$A$1:$E$2</definedName>
-    <definedName function="false" hidden="true" localSheetId="18" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_H2SO4-cmp'!$A$1:$E$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="10" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_fe-mat'!$A$1:$E$4</definedName>
     <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_liquids-mat'!$A$1:$E$2</definedName>
-    <definedName function="false" hidden="true" localSheetId="8" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_nonferrous-mat'!$A$1:$E$4</definedName>
-    <definedName function="false" hidden="true" localSheetId="19" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_Pb-elm'!$A$1:$E$2</definedName>
-    <definedName function="false" hidden="true" localSheetId="17" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_plastic-mat'!$A$1:$E$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="8" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_nfe-mat'!$A$1:$E$3</definedName>
     <definedName function="false" hidden="true" localSheetId="13" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_ree-mat'!$A$1:$E$2</definedName>
-    <definedName function="false" hidden="true" localSheetId="12" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_rubber-mat'!$A$1:$E$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="20" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_rest-mat'!$A$1:$E$2</definedName>
     <definedName function="false" hidden="true" localSheetId="11" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_slag_fe-mat'!$A$1:$E$4</definedName>
-    <definedName function="false" hidden="true" localSheetId="9" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_slag_nfe-mat'!$A$1:$E$4</definedName>
-    <definedName function="false" hidden="true" localSheetId="14" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_slag_ree-mat'!$A$1:$E$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="9" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_slag_nfe-mat'!$A$1:$E$3</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_tyres-cpt'!$A$1:$E$3</definedName>
     <definedName function="false" hidden="true" localSheetId="16" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_waste_shredder-mat'!$A$1:$E$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="21" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_wasteoil-mat'!$A$1:$E$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="18" name="_xlnm._FilterDatabase" vbProcedure="false">'H2SO4-cmp'!$A$1:$E$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="19" name="_xlnm._FilterDatabase" vbProcedure="false">'Pb-elm'!$A$1:$E$2</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -60,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="42">
   <si>
     <t xml:space="preserve">fraction</t>
   </si>
@@ -77,52 +81,52 @@
     <t xml:space="preserve">uncertainty</t>
   </si>
   <si>
-    <t xml:space="preserve">ICE_body</t>
+    <t xml:space="preserve">ELV_ICE_body</t>
   </si>
   <si>
     <t xml:space="preserve">component</t>
   </si>
   <si>
-    <t xml:space="preserve">ICE_engtrans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICE_catconverter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICE_tyres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICE_elec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICE_batt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICE_liquids</t>
+    <t xml:space="preserve">ELV_ICE_engtrans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_ICE_catconverter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_ICE_tyres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_ICE_elec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_ICE_batt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_ICE_liquids</t>
   </si>
   <si>
     <t xml:space="preserve">total</t>
   </si>
   <si>
-    <t xml:space="preserve">ferrous</t>
+    <t xml:space="preserve">ELV_ICE_fe</t>
   </si>
   <si>
     <t xml:space="preserve">material</t>
   </si>
   <si>
-    <t xml:space="preserve">nonferrous</t>
-  </si>
-  <si>
-    <t xml:space="preserve">glass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rubber</t>
+    <t xml:space="preserve">ELV_ICE_nfe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALL_glass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_ICE_rest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_ICE_ree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALL_rubber</t>
   </si>
   <si>
     <t xml:space="preserve">Cu</t>
@@ -152,10 +156,10 @@
     <t xml:space="preserve">Pd</t>
   </si>
   <si>
-    <t xml:space="preserve">plastic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">waste_oil</t>
+    <t xml:space="preserve">ALL_plastic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALL_waste_oil</t>
   </si>
   <si>
     <t xml:space="preserve">H2SO4</t>
@@ -164,9 +168,6 @@
     <t xml:space="preserve">compound</t>
   </si>
   <si>
-    <t xml:space="preserve">brass</t>
-  </si>
-  <si>
     <t xml:space="preserve">Zn</t>
   </si>
   <si>
@@ -186,6 +187,9 @@
   </si>
   <si>
     <t xml:space="preserve">Ce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_ICE_wasteoil</t>
   </si>
 </sst>
 </file>
@@ -362,6 +366,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
+<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing21.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
@@ -634,7 +646,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="34.47"/>
@@ -667,7 +679,7 @@
         <v>22</v>
       </c>
       <c r="C2" s="3" t="n">
-        <f aca="false">$C$11*D2</f>
+        <f aca="false">$C$10*D2</f>
         <v>19.88</v>
       </c>
       <c r="D2" s="2" t="n">
@@ -685,7 +697,7 @@
         <v>22</v>
       </c>
       <c r="C3" s="3" t="n">
-        <f aca="false">$C$11*D3</f>
+        <f aca="false">$C$10*D3</f>
         <v>3.976</v>
       </c>
       <c r="D3" s="2" t="n">
@@ -697,17 +709,17 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="3" t="n">
-        <f aca="false">$C$11*D4</f>
-        <v>3.976</v>
+        <f aca="false">$C$10*D4</f>
+        <v>1.988</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0.1</v>
@@ -715,13 +727,13 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C5" s="3" t="n">
-        <f aca="false">$C$11*D5</f>
+        <f aca="false">$C$10*D5</f>
         <v>1.988</v>
       </c>
       <c r="D5" s="2" t="n">
@@ -733,13 +745,13 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="3" t="n">
-        <f aca="false">$C$11*D6</f>
+        <f aca="false">$C$10*D6</f>
         <v>1.988</v>
       </c>
       <c r="D6" s="2" t="n">
@@ -751,88 +763,73 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C7" s="3" t="n">
-        <f aca="false">$C$11*D7</f>
+        <f aca="false">$C$10*D7</f>
         <v>1.988</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C8" s="3" t="n">
-        <f aca="false">$C$11*D8</f>
+        <f aca="false">$C$10*D8</f>
         <v>1.988</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0.01</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>22</v>
+      <c r="A9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C9" s="3" t="n">
-        <f aca="false">$C$11*D9</f>
-        <v>1.988</v>
+        <f aca="false">$C$10*D9</f>
+        <v>161.028</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.01</v>
+        <v>0.81</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C10" s="3" t="n">
-        <f aca="false">$C$11*D10</f>
-        <v>161.028</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>0.81</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="3" t="n">
         <f aca="false">'ELV_ICE_engtrans-cpt'!C3+'ELV_ICE_body-cpt'!C3</f>
         <v>198.8</v>
       </c>
-      <c r="D11" s="2" t="n">
-        <f aca="false">SUM(D2:D10)</f>
-        <v>1</v>
-      </c>
+      <c r="D10" s="2" t="n">
+        <f aca="false">SUM(D2:D9)</f>
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C12" s="3"/>
@@ -840,11 +837,8 @@
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C13" s="3"/>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="3"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E4"/>
+  <autoFilter ref="A1:E3"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -888,7 +882,7 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>22</v>
@@ -924,7 +918,7 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>22</v>
@@ -1025,7 +1019,7 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>22</v>
@@ -1061,7 +1055,7 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>22</v>
@@ -1243,7 +1237,7 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>22</v>
@@ -1279,7 +1273,7 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>22</v>
@@ -1297,7 +1291,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>22</v>
@@ -2092,6 +2086,150 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="34.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="2" width="16.69"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <f aca="false">SUM(D2:D2)</f>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E2"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="34.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="2" width="16.69"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <f aca="false">SUM(D2:D2)</f>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E2"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -2918,7 +3056,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="34.47"/>
@@ -2951,7 +3089,7 @@
         <v>22</v>
       </c>
       <c r="C2" s="3" t="n">
-        <f aca="false">$C$11*D2</f>
+        <f aca="false">$C$10*D2</f>
         <v>109.34</v>
       </c>
       <c r="D2" s="2" t="n">
@@ -2969,7 +3107,7 @@
         <v>22</v>
       </c>
       <c r="C3" s="3" t="n">
-        <f aca="false">$C$11*D3</f>
+        <f aca="false">$C$10*D3</f>
         <v>29.82</v>
       </c>
       <c r="D3" s="2" t="n">
@@ -2981,17 +3119,17 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="3" t="n">
-        <f aca="false">$C$11*D4</f>
-        <v>15.904</v>
+        <f aca="false">$C$10*D4</f>
+        <v>5.964</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0.1</v>
@@ -2999,13 +3137,13 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C5" s="3" t="n">
-        <f aca="false">$C$11*D5</f>
+        <f aca="false">$C$10*D5</f>
         <v>5.964</v>
       </c>
       <c r="D5" s="2" t="n">
@@ -3017,17 +3155,17 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="3" t="n">
-        <f aca="false">$C$11*D6</f>
-        <v>5.964</v>
+        <f aca="false">$C$10*D6</f>
+        <v>3.976</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0.1</v>
@@ -3035,88 +3173,73 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C7" s="3" t="n">
-        <f aca="false">$C$11*D7</f>
+        <f aca="false">$C$10*D7</f>
         <v>3.976</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0.02</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C8" s="3" t="n">
-        <f aca="false">$C$11*D8</f>
+        <f aca="false">$C$10*D8</f>
         <v>3.976</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0.02</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>22</v>
+      <c r="A9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="C9" s="3" t="n">
-        <f aca="false">$C$11*D9</f>
-        <v>3.976</v>
+        <f aca="false">$C$10*D9</f>
+        <v>19.88</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C10" s="3" t="n">
-        <f aca="false">$C$11*D10</f>
-        <v>19.88</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="3" t="n">
         <f aca="false">'ELV_ICE_engtrans-cpt'!C3+'ELV_ICE_body-cpt'!C3</f>
         <v>198.8</v>
       </c>
-      <c r="D11" s="2" t="n">
-        <f aca="false">SUM(D2:D10)</f>
-        <v>1</v>
-      </c>
+      <c r="D10" s="2" t="n">
+        <f aca="false">SUM(D2:D9)</f>
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C12" s="3"/>
@@ -3124,11 +3247,8 @@
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C13" s="3"/>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="3"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E4"/>
+  <autoFilter ref="A1:E3"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/src/examples/ELV/data/ELV_ICE_compositions.xlsx
+++ b/src/examples/ELV/data/ELV_ICE_compositions.xlsx
@@ -5,54 +5,56 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="13"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="ELV_ICE-prd" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="ELV_ICE_body-cpt" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="ELV_ICE_engtrans-cpt" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="ELV_ICE_catconv-cpt" sheetId="4" state="visible" r:id="rId5"/>
-    <sheet name="ELV_ICE_tyres-cpt" sheetId="5" state="visible" r:id="rId6"/>
-    <sheet name="ELV_ICE_elec-cpt" sheetId="6" state="visible" r:id="rId7"/>
-    <sheet name="ELV_ICE_liquids-mat" sheetId="7" state="visible" r:id="rId8"/>
-    <sheet name="ELV_ICE_batt-cpt" sheetId="8" state="visible" r:id="rId9"/>
-    <sheet name="ELV_ICE_nfe-mat" sheetId="9" state="visible" r:id="rId10"/>
-    <sheet name="ELV_ICE_slag_nfe-mat" sheetId="10" state="visible" r:id="rId11"/>
-    <sheet name="ELV_ICE_fe-mat" sheetId="11" state="visible" r:id="rId12"/>
-    <sheet name="ELV_ICE_slag_fe-mat" sheetId="12" state="visible" r:id="rId13"/>
-    <sheet name="ALL_rubber-mat" sheetId="13" state="visible" r:id="rId14"/>
-    <sheet name="ELV_ICE_ree-mat" sheetId="14" state="visible" r:id="rId15"/>
-    <sheet name="ALL_slag_ree-mat" sheetId="15" state="visible" r:id="rId16"/>
-    <sheet name="ALL_glass-mat" sheetId="16" state="visible" r:id="rId17"/>
-    <sheet name="ELV_ICE_waste_shredder-mat" sheetId="17" state="visible" r:id="rId18"/>
-    <sheet name="ALL_plastic-mat" sheetId="18" state="visible" r:id="rId19"/>
-    <sheet name="H2SO4-cmp" sheetId="19" state="visible" r:id="rId20"/>
-    <sheet name="Pb-elm" sheetId="20" state="visible" r:id="rId21"/>
-    <sheet name="ELV_ICE_rest-mat" sheetId="21" state="visible" r:id="rId22"/>
-    <sheet name="ELV_ICE_wasteoil-mat" sheetId="22" state="visible" r:id="rId23"/>
+    <sheet name="NEW_ICE-prd" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="ELV_ICE_parts-prd" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="ELV_ICE_body-cpt" sheetId="4" state="visible" r:id="rId5"/>
+    <sheet name="ELV_ICE_engtrans-cpt" sheetId="5" state="visible" r:id="rId6"/>
+    <sheet name="ELV_ICE_catconv-cpt" sheetId="6" state="visible" r:id="rId7"/>
+    <sheet name="ELV_ICE_tyres-cpt" sheetId="7" state="visible" r:id="rId8"/>
+    <sheet name="ELV_ICE_elec-cpt" sheetId="8" state="visible" r:id="rId9"/>
+    <sheet name="ELV_ICE_liquids-mat" sheetId="9" state="visible" r:id="rId10"/>
+    <sheet name="ELV_ICE_batt-cpt" sheetId="10" state="visible" r:id="rId11"/>
+    <sheet name="ELV_ICE_nfe-mat" sheetId="11" state="visible" r:id="rId12"/>
+    <sheet name="ELV_ICE_slag_nfe-mat" sheetId="12" state="visible" r:id="rId13"/>
+    <sheet name="ELV_ICE_fe-mat" sheetId="13" state="visible" r:id="rId14"/>
+    <sheet name="ELV_ICE_slag_fe-mat" sheetId="14" state="visible" r:id="rId15"/>
+    <sheet name="ALL_rubber-mat" sheetId="15" state="visible" r:id="rId16"/>
+    <sheet name="ELV_ICE_ree-mat" sheetId="16" state="visible" r:id="rId17"/>
+    <sheet name="ALL_slag_ree-mat" sheetId="17" state="visible" r:id="rId18"/>
+    <sheet name="ALL_glass-mat" sheetId="18" state="visible" r:id="rId19"/>
+    <sheet name="ELV_ICE_waste_shredder-mat" sheetId="19" state="visible" r:id="rId20"/>
+    <sheet name="ALL_plastic-mat" sheetId="20" state="visible" r:id="rId21"/>
+    <sheet name="H2SO4-cmp" sheetId="21" state="visible" r:id="rId22"/>
+    <sheet name="Pb-elm" sheetId="22" state="visible" r:id="rId23"/>
+    <sheet name="ELV_ICE_rest-mat" sheetId="23" state="visible" r:id="rId24"/>
+    <sheet name="ELV_ICE_wasteoil-mat" sheetId="24" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="15" name="_xlnm._FilterDatabase" vbProcedure="false">'ALL_glass-mat'!$A$1:$E$2</definedName>
-    <definedName function="false" hidden="true" localSheetId="17" name="_xlnm._FilterDatabase" vbProcedure="false">'ALL_plastic-mat'!$A$1:$E$2</definedName>
-    <definedName function="false" hidden="true" localSheetId="12" name="_xlnm._FilterDatabase" vbProcedure="false">'ALL_rubber-mat'!$A$1:$E$2</definedName>
-    <definedName function="false" hidden="true" localSheetId="14" name="_xlnm._FilterDatabase" vbProcedure="false">'ALL_slag_ree-mat'!$A$1:$E$2</definedName>
-    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_batt-cpt'!$A$1:$E$3</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_body-cpt'!$A$1:$E$5</definedName>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_catconv-cpt'!$A$1:$E$2</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_elec-cpt'!$A$1:$E$4</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_engtrans-cpt'!$A$1:$E$4</definedName>
-    <definedName function="false" hidden="true" localSheetId="10" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_fe-mat'!$A$1:$E$4</definedName>
-    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_liquids-mat'!$A$1:$E$2</definedName>
-    <definedName function="false" hidden="true" localSheetId="8" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_nfe-mat'!$A$1:$E$3</definedName>
-    <definedName function="false" hidden="true" localSheetId="13" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_ree-mat'!$A$1:$E$2</definedName>
-    <definedName function="false" hidden="true" localSheetId="20" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_rest-mat'!$A$1:$E$2</definedName>
-    <definedName function="false" hidden="true" localSheetId="11" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_slag_fe-mat'!$A$1:$E$4</definedName>
-    <definedName function="false" hidden="true" localSheetId="9" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_slag_nfe-mat'!$A$1:$E$3</definedName>
-    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_tyres-cpt'!$A$1:$E$3</definedName>
-    <definedName function="false" hidden="true" localSheetId="16" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_waste_shredder-mat'!$A$1:$E$2</definedName>
-    <definedName function="false" hidden="true" localSheetId="21" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_wasteoil-mat'!$A$1:$E$2</definedName>
-    <definedName function="false" hidden="true" localSheetId="18" name="_xlnm._FilterDatabase" vbProcedure="false">'H2SO4-cmp'!$A$1:$E$2</definedName>
-    <definedName function="false" hidden="true" localSheetId="19" name="_xlnm._FilterDatabase" vbProcedure="false">'Pb-elm'!$A$1:$E$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="17" name="_xlnm._FilterDatabase" vbProcedure="false">'ALL_glass-mat'!$A$1:$E$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="19" name="_xlnm._FilterDatabase" vbProcedure="false">'ALL_plastic-mat'!$A$1:$E$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="14" name="_xlnm._FilterDatabase" vbProcedure="false">'ALL_rubber-mat'!$A$1:$E$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="16" name="_xlnm._FilterDatabase" vbProcedure="false">'ALL_slag_ree-mat'!$A$1:$E$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="9" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_batt-cpt'!$A$1:$E$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_body-cpt'!$A$1:$E$5</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_catconv-cpt'!$A$1:$E$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_elec-cpt'!$A$1:$E$4</definedName>
+    <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_engtrans-cpt'!$A$1:$E$4</definedName>
+    <definedName function="false" hidden="true" localSheetId="12" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_fe-mat'!$A$1:$E$4</definedName>
+    <definedName function="false" hidden="true" localSheetId="8" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_liquids-mat'!$A$1:$E$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="10" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_nfe-mat'!$A$1:$E$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="15" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_ree-mat'!$A$1:$E$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="22" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_rest-mat'!$A$1:$E$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="13" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_slag_fe-mat'!$A$1:$E$4</definedName>
+    <definedName function="false" hidden="true" localSheetId="11" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_slag_nfe-mat'!$A$1:$E$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_tyres-cpt'!$A$1:$E$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="18" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_waste_shredder-mat'!$A$1:$E$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="23" name="_xlnm._FilterDatabase" vbProcedure="false">'ELV_ICE_wasteoil-mat'!$A$1:$E$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="20" name="_xlnm._FilterDatabase" vbProcedure="false">'H2SO4-cmp'!$A$1:$E$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="21" name="_xlnm._FilterDatabase" vbProcedure="false">'Pb-elm'!$A$1:$E$2</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -64,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="42">
   <si>
     <t xml:space="preserve">fraction</t>
   </si>
@@ -90,7 +92,7 @@
     <t xml:space="preserve">ELV_ICE_engtrans</t>
   </si>
   <si>
-    <t xml:space="preserve">ELV_ICE_catconverter</t>
+    <t xml:space="preserve">ELV_ICE_catconv</t>
   </si>
   <si>
     <t xml:space="preserve">ELV_ICE_tyres</t>
@@ -646,6 +648,334 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="34.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="2" width="16.69"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="2" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <f aca="false">C$5*D2</f>
+        <v>18.2</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <f aca="false">C$5*D3</f>
+        <v>7</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <f aca="false">C$5*D4</f>
+        <v>2.8</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <f aca="false">'ELV_ICE-prd'!C$7</f>
+        <v>28</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <f aca="false">SUM(D2:D4)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C8" s="3"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E3"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="34.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="2" width="16.69"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="2" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <f aca="false">$C$10*D2</f>
+        <v>109.34</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <f aca="false">$C$10*D3</f>
+        <v>29.82</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <f aca="false">$C$10*D4</f>
+        <v>5.964</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <f aca="false">$C$10*D5</f>
+        <v>5.964</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <f aca="false">$C$10*D6</f>
+        <v>3.976</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <f aca="false">$C$10*D7</f>
+        <v>3.976</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <f aca="false">$C$10*D8</f>
+        <v>3.976</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <f aca="false">$C$10*D9</f>
+        <v>35.784</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <f aca="false">'ELV_ICE_engtrans-cpt'!C3+'ELV_ICE_body-cpt'!C3</f>
+        <v>198.8</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <f aca="false">SUM(D2:D9)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C13" s="3"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E3"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:E13"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -806,10 +1136,10 @@
       </c>
       <c r="C9" s="3" t="n">
         <f aca="false">$C$10*D9</f>
-        <v>161.028</v>
+        <v>165.004</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.81</v>
+        <v>0.83</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>3.1</v>
@@ -825,7 +1155,7 @@
       </c>
       <c r="D10" s="2" t="n">
         <f aca="false">SUM(D2:D9)</f>
-        <v>0.98</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -850,7 +1180,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -987,7 +1317,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1124,7 +1454,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1205,7 +1535,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1350,7 +1680,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1463,205 +1793,6 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C11" s="3"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:E2"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
-  </headerFooter>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="34.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="2" width="16.69"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="11.53"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <f aca="false">SUM(D2:D2)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="3"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C5" s="3"/>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C6" s="3"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:E2"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
-  </headerFooter>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="34.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="2" width="16.69"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="11.53"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <f aca="false">D2*$C$5</f>
-        <v>60.9</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <f aca="false">D3*$C$5</f>
-        <v>20.3</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <f aca="false">D4*$C$5</f>
-        <v>20.3</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>101.5</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <f aca="false">SUM(D2:D4)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C6" s="3"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="3"/>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C8" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E2"/>
@@ -1708,13 +1839,13 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>30.8</v>
+        <v>60.5</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>1</v>
@@ -1728,7 +1859,7 @@
         <v>13</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>30.8</v>
+        <v>60.5</v>
       </c>
       <c r="D3" s="2" t="n">
         <f aca="false">SUM(D2:D2)</f>
@@ -1762,7 +1893,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="34.47"/>
@@ -1789,32 +1920,78 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>7</v>
+        <f aca="false">D2*$C$5</f>
+        <v>60.9</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <f aca="false">D3*$C$5</f>
+        <v>20.3</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <f aca="false">D4*$C$5</f>
+        <v>20.3</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <f aca="false">SUM(D2:D2)</f>
-        <v>1</v>
-      </c>
+      <c r="C5" s="3" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <f aca="false">SUM(D2:D4)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C8" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E2"/>
@@ -1834,7 +2011,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.47"/>
@@ -1863,17 +2040,16 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <f aca="false">'ELV_ICE-prd'!C$2*D2</f>
-        <v>485.1</v>
+        <v>770</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.63</v>
+        <v>0.55</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0.1</v>
@@ -1884,17 +2060,16 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3" t="n">
-        <f aca="false">'ELV_ICE-prd'!C$2*D3</f>
-        <v>169.4</v>
+        <v>420</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0.1</v>
@@ -1904,18 +2079,17 @@
       <c r="H3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>15</v>
+      <c r="A4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="n">
-        <f aca="false">'ELV_ICE-prd'!C$2*D4</f>
-        <v>30.8</v>
+        <v>70</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>0.1</v>
@@ -1925,18 +2099,17 @@
       <c r="H4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>18</v>
+      <c r="A5" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C5" s="3" t="n">
-        <f aca="false">'ELV_ICE-prd'!C$2*D5</f>
-        <v>84.7</v>
+        <v>56</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.11</v>
+        <v>0.04</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0.1</v>
@@ -1946,51 +2119,102 @@
       <c r="H5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="2"/>
+      <c r="A6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="C6" s="3" t="n">
-        <f aca="false">'ELV_ICE-prd'!C2</f>
-        <v>770</v>
+        <v>28</v>
       </c>
       <c r="D6" s="2" t="n">
-        <f aca="false">SUM(D2:D5)</f>
-        <v>1</v>
-      </c>
-      <c r="E6" s="2"/>
+        <v>0.02</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0.1</v>
+      </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="A7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0.1</v>
+      </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="A8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.1</v>
+      </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
     </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="3" t="n">
+        <f aca="false">SUM(C2:C8)</f>
+        <v>1400</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <f aca="false">SUM(D2:D8)</f>
+        <v>1</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+    </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="4"/>
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="4"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C12" s="4"/>
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C13" s="4"/>
@@ -2001,8 +2225,16 @@
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C15" s="4"/>
     </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C16" s="4"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C17" s="4"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="4"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E5"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2010,7 +2242,6 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2019,7 +2250,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="34.47"/>
@@ -2046,19 +2277,19 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>18</v>
+        <v>30.8</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2066,12 +2297,21 @@
         <v>13</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>18</v>
+        <v>30.8</v>
       </c>
       <c r="D3" s="2" t="n">
         <f aca="false">SUM(D2:D2)</f>
         <v>1</v>
       </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C4" s="3"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C5" s="3"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C6" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E2"/>
@@ -2118,13 +2358,13 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>1</v>
@@ -2138,7 +2378,7 @@
         <v>13</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D3" s="2" t="n">
         <f aca="false">SUM(D2:D2)</f>
@@ -2190,13 +2430,13 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>1</v>
@@ -2210,7 +2450,7 @@
         <v>13</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D3" s="2" t="n">
         <f aca="false">SUM(D2:D2)</f>
@@ -2230,7 +2470,475 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="34.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="2" width="16.69"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <f aca="false">SUM(D2:D2)</f>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E2"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="34.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="2" width="16.69"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <f aca="false">SUM(D2:D2)</f>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E2"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="16.69"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>770</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>420</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="3" t="n">
+        <f aca="false">SUM(C2:C3)</f>
+        <v>1190</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <f aca="false">SUM(D2:D3)</f>
+        <v>1</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C10" s="4"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C13" s="4"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="16.69"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <f aca="false">'ELV_ICE-prd'!C$2*D2</f>
+        <v>485.1</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <f aca="false">'ELV_ICE-prd'!C$2*D3</f>
+        <v>169.4</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <f aca="false">'ELV_ICE-prd'!C$2*D4</f>
+        <v>30.8</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <f aca="false">'ELV_ICE-prd'!C$2*D5</f>
+        <v>84.7</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="3" t="n">
+        <f aca="false">'ELV_ICE-prd'!C2</f>
+        <v>770</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <f aca="false">SUM(D2:D5)</f>
+        <v>1</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C10" s="4"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C15" s="4"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E5"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2394,7 +3102,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2522,7 +3230,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2623,7 +3331,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2850,7 +3558,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2930,332 +3638,4 @@
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="34.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="2" width="16.69"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="2" width="11.53"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <f aca="false">C$5*D2</f>
-        <v>18.2</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <f aca="false">C$5*D3</f>
-        <v>7</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <f aca="false">C$5*D4</f>
-        <v>2.8</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <f aca="false">'ELV_ICE-prd'!C$7</f>
-        <v>28</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <f aca="false">SUM(D2:D4)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C6" s="3"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="3"/>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C8" s="3"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:E3"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
-  </headerFooter>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:E13"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="34.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="2" width="16.69"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="2" width="11.53"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <f aca="false">$C$10*D2</f>
-        <v>109.34</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <f aca="false">$C$10*D3</f>
-        <v>29.82</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <f aca="false">$C$10*D4</f>
-        <v>5.964</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <f aca="false">$C$10*D5</f>
-        <v>5.964</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <f aca="false">$C$10*D6</f>
-        <v>3.976</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <f aca="false">$C$10*D7</f>
-        <v>3.976</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <f aca="false">$C$10*D8</f>
-        <v>3.976</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <f aca="false">$C$10*D9</f>
-        <v>19.88</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <f aca="false">'ELV_ICE_engtrans-cpt'!C3+'ELV_ICE_body-cpt'!C3</f>
-        <v>198.8</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <f aca="false">SUM(D2:D9)</f>
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="3"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="3"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:E3"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
-  </headerFooter>
-  <drawing r:id="rId1"/>
-</worksheet>
 </file>
--- a/src/examples/ELV/data/ELV_ICE_compositions.xlsx
+++ b/src/examples/ELV/data/ELV_ICE_compositions.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="10"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="ELV_ICE-prd" sheetId="1" state="visible" r:id="rId2"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="44">
   <si>
     <t xml:space="preserve">fraction</t>
   </si>
@@ -108,6 +108,12 @@
   </si>
   <si>
     <t xml:space="preserve">total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELV_ICE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">product</t>
   </si>
   <si>
     <t xml:space="preserve">ELV_ICE_fe</t>
@@ -675,10 +681,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3" t="n">
         <f aca="false">C$5*D2</f>
@@ -693,10 +699,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C3" s="3" t="n">
         <f aca="false">C$5*D3</f>
@@ -711,10 +717,10 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="3" t="n">
         <f aca="false">C$5*D4</f>
@@ -794,10 +800,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3" t="n">
         <f aca="false">$C$10*D2</f>
@@ -812,10 +818,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C3" s="3" t="n">
         <f aca="false">$C$10*D3</f>
@@ -830,10 +836,10 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C4" s="3" t="n">
         <f aca="false">$C$10*D4</f>
@@ -848,10 +854,10 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3" t="n">
         <f aca="false">$C$10*D5</f>
@@ -866,10 +872,10 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C6" s="3" t="n">
         <f aca="false">$C$10*D6</f>
@@ -884,10 +890,10 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C7" s="3" t="n">
         <f aca="false">$C$10*D7</f>
@@ -902,10 +908,10 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" s="3" t="n">
         <f aca="false">$C$10*D8</f>
@@ -920,10 +926,10 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" s="3" t="n">
         <f aca="false">$C$10*D9</f>
@@ -1003,10 +1009,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3" t="n">
         <f aca="false">$C$10*D2</f>
@@ -1021,10 +1027,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C3" s="3" t="n">
         <f aca="false">$C$10*D3</f>
@@ -1039,10 +1045,10 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C4" s="3" t="n">
         <f aca="false">$C$10*D4</f>
@@ -1057,10 +1063,10 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3" t="n">
         <f aca="false">$C$10*D5</f>
@@ -1075,10 +1081,10 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C6" s="3" t="n">
         <f aca="false">$C$10*D6</f>
@@ -1093,10 +1099,10 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C7" s="3" t="n">
         <f aca="false">$C$10*D7</f>
@@ -1111,10 +1117,10 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" s="3" t="n">
         <f aca="false">$C$10*D8</f>
@@ -1129,10 +1135,10 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" s="3" t="n">
         <f aca="false">$C$10*D9</f>
@@ -1212,10 +1218,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3" t="n">
         <f aca="false">$C$6*D2</f>
@@ -1230,10 +1236,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C3" s="3" t="n">
         <f aca="false">$C$6*D3</f>
@@ -1248,10 +1254,10 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C4" s="3" t="n">
         <f aca="false">$C$6*D4</f>
@@ -1266,10 +1272,10 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3" t="n">
         <f aca="false">$C$6*D5</f>
@@ -1349,10 +1355,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3" t="n">
         <f aca="false">$C$6*D2</f>
@@ -1367,10 +1373,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C3" s="3" t="n">
         <f aca="false">$C$6*D3</f>
@@ -1385,10 +1391,10 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C4" s="3" t="n">
         <f aca="false">$C$6*D4</f>
@@ -1403,10 +1409,10 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3" t="n">
         <f aca="false">$C$6*D5</f>
@@ -1486,10 +1492,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>4.2</v>
@@ -1567,10 +1573,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3" t="n">
         <f aca="false">D2*$C$7</f>
@@ -1585,10 +1591,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C3" s="3" t="n">
         <f aca="false">D3*$C$7</f>
@@ -1603,10 +1609,10 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C4" s="3" t="n">
         <f aca="false">D4*$C$7</f>
@@ -1621,10 +1627,10 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3" t="n">
         <f aca="false">D5*$C$7</f>
@@ -1639,10 +1645,10 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C6" s="3" t="n">
         <f aca="false">D6*$C$7</f>
@@ -1712,10 +1718,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C2" s="1" t="n">
         <f aca="false">0.31*70</f>
@@ -1730,10 +1736,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3" s="3" t="n">
         <f aca="false">'ELV_ICE-prd'!C$4*D3</f>
@@ -1748,10 +1754,10 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="3" t="n">
         <f aca="false">'ELV_ICE-prd'!C$4*D4</f>
@@ -1839,10 +1845,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>15</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>60.5</v>
@@ -1920,10 +1926,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="n">
         <f aca="false">D2*$C$5</f>
@@ -1938,10 +1944,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3" s="3" t="n">
         <f aca="false">D3*$C$5</f>
@@ -1956,10 +1962,10 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="3" t="n">
         <f aca="false">D4*$C$5</f>
@@ -2011,7 +2017,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.47"/>
@@ -2040,10 +2046,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>770</v>
@@ -2059,180 +2065,60 @@
       <c r="H2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>6</v>
-      </c>
+      <c r="A3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="2"/>
       <c r="C3" s="3" t="n">
-        <v>420</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0.1</v>
-      </c>
+        <f aca="false">SUM(C2:C2)</f>
+        <v>770</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <f aca="false">SUM(D2:D2)</f>
+        <v>0.55</v>
+      </c>
+      <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-    </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
+      <c r="C7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
+      <c r="C8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="3" t="n">
-        <f aca="false">SUM(C2:C8)</f>
-        <v>1400</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <f aca="false">SUM(D2:D8)</f>
-        <v>1</v>
-      </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
+      <c r="C9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
+      <c r="C10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="4"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="4"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C15" s="4"/>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C16" s="4"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C17" s="4"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="4"/>
+      <c r="C11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C12" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2277,10 +2163,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>30.8</v>
@@ -2358,10 +2244,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>7</v>
@@ -2430,10 +2316,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>18</v>
@@ -2502,10 +2388,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>18</v>
@@ -2574,10 +2460,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>10</v>
@@ -2787,10 +2673,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="n">
         <f aca="false">'ELV_ICE-prd'!C$2*D2</f>
@@ -2808,10 +2694,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3" s="3" t="n">
         <f aca="false">'ELV_ICE-prd'!C$2*D3</f>
@@ -2829,10 +2715,10 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="C4" s="3" t="n">
         <f aca="false">'ELV_ICE-prd'!C$2*D4</f>
@@ -2850,10 +2736,10 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3" t="n">
         <f aca="false">'ELV_ICE-prd'!C$2*D5</f>
@@ -2972,10 +2858,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="n">
         <f aca="false">'ELV_ICE-prd'!C$3*D2</f>
@@ -2993,10 +2879,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3" s="3" t="n">
         <f aca="false">'ELV_ICE-prd'!C$3*D3</f>
@@ -3014,10 +2900,10 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="3" t="n">
         <f aca="false">'ELV_ICE-prd'!C$3*D4</f>
@@ -3134,10 +3020,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C2" s="1" t="n">
         <f aca="false">0.31*70</f>
@@ -3152,10 +3038,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3" s="3" t="n">
         <f aca="false">'ELV_ICE-prd'!C$4*D3</f>
@@ -3170,10 +3056,10 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="3" t="n">
         <f aca="false">'ELV_ICE-prd'!C$4*D4</f>
@@ -3262,10 +3148,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="n">
         <f aca="false">$C$4*D2</f>
@@ -3280,10 +3166,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3" s="3" t="n">
         <f aca="false">$C$4*D3</f>
@@ -3363,10 +3249,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3" t="n">
         <f aca="false">'ELV_ICE-prd'!C$6*D2</f>
@@ -3381,10 +3267,10 @@
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C3" s="3" t="n">
         <f aca="false">'ELV_ICE-prd'!C$6*D3</f>
@@ -3399,10 +3285,10 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="C4" s="3" t="n">
         <f aca="false">'ELV_ICE-prd'!C$6*D4</f>
@@ -3417,10 +3303,10 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3" t="n">
         <f aca="false">'ELV_ICE-prd'!C$6*D5</f>
@@ -3435,10 +3321,10 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C6" s="3" t="n">
         <f aca="false">'ELV_ICE-prd'!C$6*D6</f>
@@ -3453,10 +3339,10 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C7" s="3" t="n">
         <f aca="false">'ELV_ICE-prd'!C$6*D7</f>
@@ -3471,10 +3357,10 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" s="3" t="n">
         <f aca="false">'ELV_ICE-prd'!C$6*D8</f>
@@ -3489,10 +3375,10 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9" s="3" t="n">
         <f aca="false">'ELV_ICE-prd'!C$6*D9</f>
@@ -3507,10 +3393,10 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C10" s="3" t="n">
         <f aca="false">'ELV_ICE-prd'!C$6*D10</f>
@@ -3590,10 +3476,10 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>28</v>
